--- a/AI4SkIN_df.xlsx
+++ b/AI4SkIN_df.xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pabmees\PycharmProjects\AI4SkIN_leaderboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D95370B-3186-4E56-81BB-65D72C97CE3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{434DEB1E-A39C-407C-AC3D-F01E2B7EE066}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2509" uniqueCount="1231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2510" uniqueCount="1232">
   <si>
     <t>WSI</t>
   </si>
@@ -3713,6 +3726,9 @@
   </si>
   <si>
     <t>GT</t>
+  </si>
+  <si>
+    <t>fold</t>
   </si>
 </sst>
 </file>
@@ -4081,7 +4097,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E627"/>
+  <dimension ref="A1:F627"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.42578125" bestFit="1" customWidth="1"/>
@@ -4091,7 +4107,7 @@
     <col min="5" max="5" width="3.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4107,8 +4123,11 @@
       <c r="E1" t="s">
         <v>1230</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" t="s">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -4124,8 +4143,11 @@
       <c r="E2">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -4141,8 +4163,11 @@
       <c r="E3">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -4158,8 +4183,11 @@
       <c r="E4">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -4175,8 +4203,11 @@
       <c r="E5">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -4192,8 +4223,11 @@
       <c r="E6">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -4209,8 +4243,11 @@
       <c r="E7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -4226,8 +4263,11 @@
       <c r="E8">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -4243,8 +4283,11 @@
       <c r="E9">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -4260,8 +4303,11 @@
       <c r="E10">
         <v>2</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -4277,8 +4323,11 @@
       <c r="E11">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -4294,8 +4343,11 @@
       <c r="E12">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -4311,8 +4363,11 @@
       <c r="E13">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -4328,8 +4383,11 @@
       <c r="E14">
         <v>2</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -4345,8 +4403,11 @@
       <c r="E15">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -4362,8 +4423,11 @@
       <c r="E16">
         <v>5</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -4379,8 +4443,11 @@
       <c r="E17">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -4396,8 +4463,11 @@
       <c r="E18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -4413,8 +4483,11 @@
       <c r="E19">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -4430,8 +4503,11 @@
       <c r="E20">
         <v>2</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -4447,8 +4523,11 @@
       <c r="E21">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -4464,8 +4543,11 @@
       <c r="E22">
         <v>2</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -4481,8 +4563,11 @@
       <c r="E23">
         <v>2</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>23</v>
       </c>
@@ -4498,8 +4583,11 @@
       <c r="E24">
         <v>2</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F24">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -4515,8 +4603,11 @@
       <c r="E25">
         <v>2</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -4532,8 +4623,11 @@
       <c r="E26">
         <v>2</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>26</v>
       </c>
@@ -4549,8 +4643,11 @@
       <c r="E27">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>27</v>
       </c>
@@ -4566,8 +4663,11 @@
       <c r="E28">
         <v>2</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>28</v>
       </c>
@@ -4583,8 +4683,11 @@
       <c r="E29">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F29">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>29</v>
       </c>
@@ -4600,8 +4703,11 @@
       <c r="E30">
         <v>4</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>30</v>
       </c>
@@ -4617,8 +4723,11 @@
       <c r="E31">
         <v>2</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>31</v>
       </c>
@@ -4634,8 +4743,11 @@
       <c r="E32">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>32</v>
       </c>
@@ -4651,8 +4763,11 @@
       <c r="E33">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>33</v>
       </c>
@@ -4668,8 +4783,11 @@
       <c r="E34">
         <v>4</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>34</v>
       </c>
@@ -4685,8 +4803,11 @@
       <c r="E35">
         <v>2</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>35</v>
       </c>
@@ -4702,8 +4823,11 @@
       <c r="E36">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F36">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>36</v>
       </c>
@@ -4719,8 +4843,11 @@
       <c r="E37">
         <v>4</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>37</v>
       </c>
@@ -4736,8 +4863,11 @@
       <c r="E38">
         <v>4</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>38</v>
       </c>
@@ -4753,8 +4883,11 @@
       <c r="E39">
         <v>5</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>39</v>
       </c>
@@ -4770,8 +4903,11 @@
       <c r="E40">
         <v>4</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>40</v>
       </c>
@@ -4787,8 +4923,11 @@
       <c r="E41">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>41</v>
       </c>
@@ -4804,8 +4943,11 @@
       <c r="E42">
         <v>2</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>42</v>
       </c>
@@ -4821,8 +4963,11 @@
       <c r="E43">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F43">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>43</v>
       </c>
@@ -4838,8 +4983,11 @@
       <c r="E44">
         <v>2</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>44</v>
       </c>
@@ -4855,8 +5003,11 @@
       <c r="E45">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>45</v>
       </c>
@@ -4872,8 +5023,11 @@
       <c r="E46">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F46">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>46</v>
       </c>
@@ -4889,8 +5043,11 @@
       <c r="E47">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F47">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>47</v>
       </c>
@@ -4906,8 +5063,11 @@
       <c r="E48">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>48</v>
       </c>
@@ -4923,8 +5083,11 @@
       <c r="E49">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>49</v>
       </c>
@@ -4940,8 +5103,11 @@
       <c r="E50">
         <v>5</v>
       </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>50</v>
       </c>
@@ -4957,8 +5123,11 @@
       <c r="E51">
         <v>5</v>
       </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F51">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>51</v>
       </c>
@@ -4974,8 +5143,11 @@
       <c r="E52">
         <v>2</v>
       </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>52</v>
       </c>
@@ -4991,8 +5163,11 @@
       <c r="E53">
         <v>5</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F53">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>53</v>
       </c>
@@ -5008,8 +5183,11 @@
       <c r="E54">
         <v>2</v>
       </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F54">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>54</v>
       </c>
@@ -5025,8 +5203,11 @@
       <c r="E55">
         <v>2</v>
       </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F55">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>55</v>
       </c>
@@ -5042,8 +5223,11 @@
       <c r="E56">
         <v>2</v>
       </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>56</v>
       </c>
@@ -5059,8 +5243,11 @@
       <c r="E57">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F57">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>57</v>
       </c>
@@ -5076,8 +5263,11 @@
       <c r="E58">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>58</v>
       </c>
@@ -5093,8 +5283,11 @@
       <c r="E59">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>59</v>
       </c>
@@ -5110,8 +5303,11 @@
       <c r="E60">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>60</v>
       </c>
@@ -5127,8 +5323,11 @@
       <c r="E61">
         <v>2</v>
       </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>61</v>
       </c>
@@ -5144,8 +5343,11 @@
       <c r="E62">
         <v>2</v>
       </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F62">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>62</v>
       </c>
@@ -5161,8 +5363,11 @@
       <c r="E63">
         <v>5</v>
       </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>63</v>
       </c>
@@ -5178,8 +5383,11 @@
       <c r="E64">
         <v>3</v>
       </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F64">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>64</v>
       </c>
@@ -5195,8 +5403,11 @@
       <c r="E65">
         <v>5</v>
       </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>65</v>
       </c>
@@ -5212,8 +5423,11 @@
       <c r="E66">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>66</v>
       </c>
@@ -5229,8 +5443,11 @@
       <c r="E67">
         <v>4</v>
       </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F67">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>67</v>
       </c>
@@ -5246,8 +5463,11 @@
       <c r="E68">
         <v>2</v>
       </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>68</v>
       </c>
@@ -5263,8 +5483,11 @@
       <c r="E69">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F69">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>69</v>
       </c>
@@ -5280,8 +5503,11 @@
       <c r="E70">
         <v>4</v>
       </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F70">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>70</v>
       </c>
@@ -5297,8 +5523,11 @@
       <c r="E71">
         <v>4</v>
       </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F71">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>71</v>
       </c>
@@ -5314,8 +5543,11 @@
       <c r="E72">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>72</v>
       </c>
@@ -5331,8 +5563,11 @@
       <c r="E73">
         <v>2</v>
       </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>73</v>
       </c>
@@ -5348,8 +5583,11 @@
       <c r="E74">
         <v>3</v>
       </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>74</v>
       </c>
@@ -5365,8 +5603,11 @@
       <c r="E75">
         <v>2</v>
       </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F75">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>75</v>
       </c>
@@ -5382,8 +5623,11 @@
       <c r="E76">
         <v>2</v>
       </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F76">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>76</v>
       </c>
@@ -5399,8 +5643,11 @@
       <c r="E77">
         <v>2</v>
       </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F77">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>77</v>
       </c>
@@ -5416,8 +5663,11 @@
       <c r="E78">
         <v>3</v>
       </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>78</v>
       </c>
@@ -5433,8 +5683,11 @@
       <c r="E79">
         <v>5</v>
       </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F79">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>79</v>
       </c>
@@ -5450,8 +5703,11 @@
       <c r="E80">
         <v>5</v>
       </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F80">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>80</v>
       </c>
@@ -5467,8 +5723,11 @@
       <c r="E81">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>81</v>
       </c>
@@ -5484,8 +5743,11 @@
       <c r="E82">
         <v>4</v>
       </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>82</v>
       </c>
@@ -5501,8 +5763,11 @@
       <c r="E83">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>83</v>
       </c>
@@ -5518,8 +5783,11 @@
       <c r="E84">
         <v>2</v>
       </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>84</v>
       </c>
@@ -5535,8 +5803,11 @@
       <c r="E85">
         <v>4</v>
       </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>85</v>
       </c>
@@ -5552,8 +5823,11 @@
       <c r="E86">
         <v>2</v>
       </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>86</v>
       </c>
@@ -5569,8 +5843,11 @@
       <c r="E87">
         <v>4</v>
       </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>87</v>
       </c>
@@ -5586,8 +5863,11 @@
       <c r="E88">
         <v>2</v>
       </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F88">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>88</v>
       </c>
@@ -5603,8 +5883,11 @@
       <c r="E89">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F89">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>89</v>
       </c>
@@ -5620,8 +5903,11 @@
       <c r="E90">
         <v>1</v>
       </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F90">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>90</v>
       </c>
@@ -5637,8 +5923,11 @@
       <c r="E91">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>91</v>
       </c>
@@ -5654,8 +5943,11 @@
       <c r="E92">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F92">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>92</v>
       </c>
@@ -5671,8 +5963,11 @@
       <c r="E93">
         <v>2</v>
       </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F93">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>93</v>
       </c>
@@ -5688,8 +5983,11 @@
       <c r="E94">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F94">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>94</v>
       </c>
@@ -5705,8 +6003,11 @@
       <c r="E95">
         <v>3</v>
       </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F95">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>95</v>
       </c>
@@ -5722,8 +6023,11 @@
       <c r="E96">
         <v>2</v>
       </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F96">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>96</v>
       </c>
@@ -5739,8 +6043,11 @@
       <c r="E97">
         <v>3</v>
       </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>97</v>
       </c>
@@ -5756,8 +6063,11 @@
       <c r="E98">
         <v>4</v>
       </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F98">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>98</v>
       </c>
@@ -5773,8 +6083,11 @@
       <c r="E99">
         <v>5</v>
       </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F99">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>99</v>
       </c>
@@ -5790,8 +6103,11 @@
       <c r="E100">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>100</v>
       </c>
@@ -5807,8 +6123,11 @@
       <c r="E101">
         <v>2</v>
       </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>101</v>
       </c>
@@ -5824,8 +6143,11 @@
       <c r="E102">
         <v>1</v>
       </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F102">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>102</v>
       </c>
@@ -5841,8 +6163,11 @@
       <c r="E103">
         <v>4</v>
       </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F103">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>103</v>
       </c>
@@ -5858,8 +6183,11 @@
       <c r="E104">
         <v>2</v>
       </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F104">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>104</v>
       </c>
@@ -5875,8 +6203,11 @@
       <c r="E105">
         <v>2</v>
       </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>105</v>
       </c>
@@ -5892,8 +6223,11 @@
       <c r="E106">
         <v>4</v>
       </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F106">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>106</v>
       </c>
@@ -5909,8 +6243,11 @@
       <c r="E107">
         <v>5</v>
       </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>107</v>
       </c>
@@ -5926,8 +6263,11 @@
       <c r="E108">
         <v>0</v>
       </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>108</v>
       </c>
@@ -5943,8 +6283,11 @@
       <c r="E109">
         <v>2</v>
       </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F109">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>109</v>
       </c>
@@ -5960,8 +6303,11 @@
       <c r="E110">
         <v>4</v>
       </c>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>110</v>
       </c>
@@ -5977,8 +6323,11 @@
       <c r="E111">
         <v>0</v>
       </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F111">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>111</v>
       </c>
@@ -5994,8 +6343,11 @@
       <c r="E112">
         <v>4</v>
       </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F112">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>112</v>
       </c>
@@ -6011,8 +6363,11 @@
       <c r="E113">
         <v>2</v>
       </c>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F113">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>113</v>
       </c>
@@ -6028,8 +6383,11 @@
       <c r="E114">
         <v>5</v>
       </c>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F114">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>114</v>
       </c>
@@ -6045,8 +6403,11 @@
       <c r="E115">
         <v>4</v>
       </c>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F115">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>115</v>
       </c>
@@ -6062,8 +6423,11 @@
       <c r="E116">
         <v>5</v>
       </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F116">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>116</v>
       </c>
@@ -6079,8 +6443,11 @@
       <c r="E117">
         <v>2</v>
       </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F117">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>117</v>
       </c>
@@ -6096,8 +6463,11 @@
       <c r="E118">
         <v>0</v>
       </c>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F118">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>118</v>
       </c>
@@ -6113,8 +6483,11 @@
       <c r="E119">
         <v>2</v>
       </c>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F119">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>119</v>
       </c>
@@ -6130,8 +6503,11 @@
       <c r="E120">
         <v>1</v>
       </c>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F120">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>120</v>
       </c>
@@ -6147,8 +6523,11 @@
       <c r="E121">
         <v>3</v>
       </c>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F121">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>121</v>
       </c>
@@ -6164,8 +6543,11 @@
       <c r="E122">
         <v>4</v>
       </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>122</v>
       </c>
@@ -6181,8 +6563,11 @@
       <c r="E123">
         <v>4</v>
       </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F123">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>123</v>
       </c>
@@ -6198,8 +6583,11 @@
       <c r="E124">
         <v>2</v>
       </c>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F124">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>124</v>
       </c>
@@ -6215,8 +6603,11 @@
       <c r="E125">
         <v>2</v>
       </c>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F125">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>125</v>
       </c>
@@ -6232,8 +6623,11 @@
       <c r="E126">
         <v>2</v>
       </c>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>126</v>
       </c>
@@ -6249,8 +6643,11 @@
       <c r="E127">
         <v>2</v>
       </c>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>127</v>
       </c>
@@ -6266,8 +6663,11 @@
       <c r="E128">
         <v>4</v>
       </c>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F128">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>128</v>
       </c>
@@ -6283,8 +6683,11 @@
       <c r="E129">
         <v>4</v>
       </c>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F129">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>129</v>
       </c>
@@ -6300,8 +6703,11 @@
       <c r="E130">
         <v>2</v>
       </c>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F130">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>130</v>
       </c>
@@ -6317,8 +6723,11 @@
       <c r="E131">
         <v>2</v>
       </c>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>131</v>
       </c>
@@ -6334,8 +6743,11 @@
       <c r="E132">
         <v>5</v>
       </c>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F132">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>132</v>
       </c>
@@ -6351,8 +6763,11 @@
       <c r="E133">
         <v>2</v>
       </c>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F133">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>133</v>
       </c>
@@ -6368,8 +6783,11 @@
       <c r="E134">
         <v>4</v>
       </c>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F134">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>134</v>
       </c>
@@ -6385,8 +6803,11 @@
       <c r="E135">
         <v>5</v>
       </c>
-    </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>135</v>
       </c>
@@ -6402,8 +6823,11 @@
       <c r="E136">
         <v>2</v>
       </c>
-    </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F136">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>136</v>
       </c>
@@ -6419,8 +6843,11 @@
       <c r="E137">
         <v>4</v>
       </c>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F137">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>137</v>
       </c>
@@ -6436,8 +6863,11 @@
       <c r="E138">
         <v>2</v>
       </c>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F138">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>138</v>
       </c>
@@ -6453,8 +6883,11 @@
       <c r="E139">
         <v>4</v>
       </c>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F139">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>139</v>
       </c>
@@ -6470,8 +6903,11 @@
       <c r="E140">
         <v>0</v>
       </c>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F140">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>140</v>
       </c>
@@ -6487,8 +6923,11 @@
       <c r="E141">
         <v>2</v>
       </c>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F141">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>141</v>
       </c>
@@ -6504,8 +6943,11 @@
       <c r="E142">
         <v>2</v>
       </c>
-    </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F142">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>142</v>
       </c>
@@ -6521,8 +6963,11 @@
       <c r="E143">
         <v>2</v>
       </c>
-    </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F143">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>143</v>
       </c>
@@ -6538,8 +6983,11 @@
       <c r="E144">
         <v>1</v>
       </c>
-    </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F144">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>144</v>
       </c>
@@ -6555,8 +7003,11 @@
       <c r="E145">
         <v>3</v>
       </c>
-    </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F145">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>145</v>
       </c>
@@ -6572,8 +7023,11 @@
       <c r="E146">
         <v>2</v>
       </c>
-    </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F146">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>146</v>
       </c>
@@ -6589,8 +7043,11 @@
       <c r="E147">
         <v>2</v>
       </c>
-    </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F147">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>147</v>
       </c>
@@ -6606,8 +7063,11 @@
       <c r="E148">
         <v>4</v>
       </c>
-    </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F148">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>148</v>
       </c>
@@ -6623,8 +7083,11 @@
       <c r="E149">
         <v>2</v>
       </c>
-    </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F149">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>149</v>
       </c>
@@ -6640,8 +7103,11 @@
       <c r="E150">
         <v>2</v>
       </c>
-    </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F150">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>150</v>
       </c>
@@ -6657,8 +7123,11 @@
       <c r="E151">
         <v>2</v>
       </c>
-    </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F151">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>151</v>
       </c>
@@ -6674,8 +7143,11 @@
       <c r="E152">
         <v>0</v>
       </c>
-    </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F152">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>152</v>
       </c>
@@ -6691,8 +7163,11 @@
       <c r="E153">
         <v>2</v>
       </c>
-    </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>153</v>
       </c>
@@ -6708,8 +7183,11 @@
       <c r="E154">
         <v>4</v>
       </c>
-    </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F154">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>154</v>
       </c>
@@ -6725,8 +7203,11 @@
       <c r="E155">
         <v>4</v>
       </c>
-    </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F155">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>155</v>
       </c>
@@ -6742,8 +7223,11 @@
       <c r="E156">
         <v>2</v>
       </c>
-    </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F156">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>156</v>
       </c>
@@ -6759,8 +7243,11 @@
       <c r="E157">
         <v>2</v>
       </c>
-    </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F157">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>157</v>
       </c>
@@ -6776,8 +7263,11 @@
       <c r="E158">
         <v>0</v>
       </c>
-    </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F158">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>158</v>
       </c>
@@ -6793,8 +7283,11 @@
       <c r="E159">
         <v>0</v>
       </c>
-    </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F159">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>159</v>
       </c>
@@ -6810,8 +7303,11 @@
       <c r="E160">
         <v>4</v>
       </c>
-    </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F160">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>160</v>
       </c>
@@ -6827,8 +7323,11 @@
       <c r="E161">
         <v>2</v>
       </c>
-    </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F161">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>161</v>
       </c>
@@ -6844,8 +7343,11 @@
       <c r="E162">
         <v>2</v>
       </c>
-    </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F162">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>162</v>
       </c>
@@ -6861,8 +7363,11 @@
       <c r="E163">
         <v>2</v>
       </c>
-    </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F163">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>163</v>
       </c>
@@ -6878,8 +7383,11 @@
       <c r="E164">
         <v>4</v>
       </c>
-    </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F164">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>164</v>
       </c>
@@ -6895,8 +7403,11 @@
       <c r="E165">
         <v>5</v>
       </c>
-    </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F165">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>165</v>
       </c>
@@ -6912,8 +7423,11 @@
       <c r="E166">
         <v>4</v>
       </c>
-    </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F166">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>166</v>
       </c>
@@ -6929,8 +7443,11 @@
       <c r="E167">
         <v>2</v>
       </c>
-    </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F167">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>167</v>
       </c>
@@ -6946,8 +7463,11 @@
       <c r="E168">
         <v>2</v>
       </c>
-    </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F168">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>168</v>
       </c>
@@ -6963,8 +7483,11 @@
       <c r="E169">
         <v>1</v>
       </c>
-    </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F169">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>169</v>
       </c>
@@ -6980,8 +7503,11 @@
       <c r="E170">
         <v>0</v>
       </c>
-    </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F170">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>170</v>
       </c>
@@ -6997,8 +7523,11 @@
       <c r="E171">
         <v>4</v>
       </c>
-    </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F171">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>171</v>
       </c>
@@ -7014,8 +7543,11 @@
       <c r="E172">
         <v>0</v>
       </c>
-    </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F172">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>172</v>
       </c>
@@ -7031,8 +7563,11 @@
       <c r="E173">
         <v>4</v>
       </c>
-    </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F173">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>173</v>
       </c>
@@ -7048,8 +7583,11 @@
       <c r="E174">
         <v>2</v>
       </c>
-    </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F174">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>174</v>
       </c>
@@ -7065,8 +7603,11 @@
       <c r="E175">
         <v>4</v>
       </c>
-    </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F175">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>175</v>
       </c>
@@ -7082,8 +7623,11 @@
       <c r="E176">
         <v>4</v>
       </c>
-    </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F176">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>176</v>
       </c>
@@ -7099,8 +7643,11 @@
       <c r="E177">
         <v>2</v>
       </c>
-    </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F177">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>177</v>
       </c>
@@ -7116,8 +7663,11 @@
       <c r="E178">
         <v>2</v>
       </c>
-    </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F178">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>178</v>
       </c>
@@ -7133,8 +7683,11 @@
       <c r="E179">
         <v>5</v>
       </c>
-    </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F179">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>179</v>
       </c>
@@ -7150,8 +7703,11 @@
       <c r="E180">
         <v>2</v>
       </c>
-    </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F180">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>180</v>
       </c>
@@ -7167,8 +7723,11 @@
       <c r="E181">
         <v>5</v>
       </c>
-    </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F181">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>181</v>
       </c>
@@ -7184,8 +7743,11 @@
       <c r="E182">
         <v>5</v>
       </c>
-    </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F182">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>182</v>
       </c>
@@ -7201,8 +7763,11 @@
       <c r="E183">
         <v>2</v>
       </c>
-    </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F183">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>183</v>
       </c>
@@ -7218,8 +7783,11 @@
       <c r="E184">
         <v>2</v>
       </c>
-    </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F184">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>184</v>
       </c>
@@ -7235,8 +7803,11 @@
       <c r="E185">
         <v>2</v>
       </c>
-    </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F185">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>185</v>
       </c>
@@ -7252,8 +7823,11 @@
       <c r="E186">
         <v>4</v>
       </c>
-    </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F186">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>186</v>
       </c>
@@ -7269,8 +7843,11 @@
       <c r="E187">
         <v>4</v>
       </c>
-    </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F187">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>187</v>
       </c>
@@ -7286,8 +7863,11 @@
       <c r="E188">
         <v>0</v>
       </c>
-    </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F188">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>188</v>
       </c>
@@ -7303,8 +7883,11 @@
       <c r="E189">
         <v>1</v>
       </c>
-    </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F189">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>189</v>
       </c>
@@ -7320,8 +7903,11 @@
       <c r="E190">
         <v>2</v>
       </c>
-    </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F190">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>190</v>
       </c>
@@ -7337,8 +7923,11 @@
       <c r="E191">
         <v>4</v>
       </c>
-    </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F191">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>191</v>
       </c>
@@ -7354,8 +7943,11 @@
       <c r="E192">
         <v>4</v>
       </c>
-    </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F192">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>192</v>
       </c>
@@ -7371,8 +7963,11 @@
       <c r="E193">
         <v>2</v>
       </c>
-    </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F193">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>193</v>
       </c>
@@ -7388,8 +7983,11 @@
       <c r="E194">
         <v>2</v>
       </c>
-    </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F194">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>194</v>
       </c>
@@ -7405,8 +8003,11 @@
       <c r="E195">
         <v>2</v>
       </c>
-    </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F195">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>195</v>
       </c>
@@ -7422,8 +8023,11 @@
       <c r="E196">
         <v>2</v>
       </c>
-    </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F196">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>196</v>
       </c>
@@ -7439,8 +8043,11 @@
       <c r="E197">
         <v>2</v>
       </c>
-    </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F197">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>197</v>
       </c>
@@ -7456,8 +8063,11 @@
       <c r="E198">
         <v>0</v>
       </c>
-    </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F198">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>198</v>
       </c>
@@ -7473,8 +8083,11 @@
       <c r="E199">
         <v>0</v>
       </c>
-    </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F199">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>199</v>
       </c>
@@ -7490,8 +8103,11 @@
       <c r="E200">
         <v>0</v>
       </c>
-    </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F200">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>200</v>
       </c>
@@ -7507,8 +8123,11 @@
       <c r="E201">
         <v>0</v>
       </c>
-    </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F201">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>201</v>
       </c>
@@ -7524,8 +8143,11 @@
       <c r="E202">
         <v>0</v>
       </c>
-    </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F202">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>202</v>
       </c>
@@ -7541,8 +8163,11 @@
       <c r="E203">
         <v>0</v>
       </c>
-    </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F203">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>203</v>
       </c>
@@ -7558,8 +8183,11 @@
       <c r="E204">
         <v>0</v>
       </c>
-    </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F204">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>204</v>
       </c>
@@ -7575,8 +8203,11 @@
       <c r="E205">
         <v>0</v>
       </c>
-    </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F205">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>205</v>
       </c>
@@ -7592,8 +8223,11 @@
       <c r="E206">
         <v>0</v>
       </c>
-    </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F206">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>206</v>
       </c>
@@ -7609,8 +8243,11 @@
       <c r="E207">
         <v>0</v>
       </c>
-    </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F207">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>207</v>
       </c>
@@ -7626,8 +8263,11 @@
       <c r="E208">
         <v>0</v>
       </c>
-    </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F208">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>208</v>
       </c>
@@ -7643,8 +8283,11 @@
       <c r="E209">
         <v>0</v>
       </c>
-    </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F209">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>209</v>
       </c>
@@ -7660,8 +8303,11 @@
       <c r="E210">
         <v>0</v>
       </c>
-    </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F210">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>210</v>
       </c>
@@ -7677,8 +8323,11 @@
       <c r="E211">
         <v>0</v>
       </c>
-    </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F211">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>211</v>
       </c>
@@ -7694,8 +8343,11 @@
       <c r="E212">
         <v>0</v>
       </c>
-    </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F212">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>212</v>
       </c>
@@ -7711,8 +8363,11 @@
       <c r="E213">
         <v>0</v>
       </c>
-    </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F213">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>213</v>
       </c>
@@ -7728,8 +8383,11 @@
       <c r="E214">
         <v>1</v>
       </c>
-    </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F214">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>214</v>
       </c>
@@ -7745,8 +8403,11 @@
       <c r="E215">
         <v>1</v>
       </c>
-    </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F215">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>215</v>
       </c>
@@ -7762,8 +8423,11 @@
       <c r="E216">
         <v>1</v>
       </c>
-    </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F216">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>216</v>
       </c>
@@ -7779,8 +8443,11 @@
       <c r="E217">
         <v>1</v>
       </c>
-    </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F217">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>217</v>
       </c>
@@ -7796,8 +8463,11 @@
       <c r="E218">
         <v>1</v>
       </c>
-    </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F218">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>218</v>
       </c>
@@ -7813,8 +8483,11 @@
       <c r="E219">
         <v>1</v>
       </c>
-    </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F219">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>219</v>
       </c>
@@ -7830,8 +8503,11 @@
       <c r="E220">
         <v>1</v>
       </c>
-    </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F220">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>220</v>
       </c>
@@ -7847,8 +8523,11 @@
       <c r="E221">
         <v>1</v>
       </c>
-    </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F221">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>221</v>
       </c>
@@ -7864,8 +8543,11 @@
       <c r="E222">
         <v>1</v>
       </c>
-    </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F222">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>222</v>
       </c>
@@ -7881,8 +8563,11 @@
       <c r="E223">
         <v>1</v>
       </c>
-    </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F223">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>223</v>
       </c>
@@ -7898,8 +8583,11 @@
       <c r="E224">
         <v>1</v>
       </c>
-    </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F224">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>224</v>
       </c>
@@ -7915,8 +8603,11 @@
       <c r="E225">
         <v>1</v>
       </c>
-    </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F225">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>225</v>
       </c>
@@ -7932,8 +8623,11 @@
       <c r="E226">
         <v>1</v>
       </c>
-    </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F226">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>226</v>
       </c>
@@ -7949,8 +8643,11 @@
       <c r="E227">
         <v>2</v>
       </c>
-    </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F227">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>227</v>
       </c>
@@ -7966,8 +8663,11 @@
       <c r="E228">
         <v>2</v>
       </c>
-    </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F228">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>228</v>
       </c>
@@ -7983,8 +8683,11 @@
       <c r="E229">
         <v>2</v>
       </c>
-    </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F229">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>229</v>
       </c>
@@ -8000,8 +8703,11 @@
       <c r="E230">
         <v>2</v>
       </c>
-    </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F230">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>230</v>
       </c>
@@ -8017,8 +8723,11 @@
       <c r="E231">
         <v>2</v>
       </c>
-    </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F231">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>231</v>
       </c>
@@ -8034,8 +8743,11 @@
       <c r="E232">
         <v>2</v>
       </c>
-    </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F232">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>232</v>
       </c>
@@ -8051,8 +8763,11 @@
       <c r="E233">
         <v>2</v>
       </c>
-    </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F233">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>233</v>
       </c>
@@ -8068,8 +8783,11 @@
       <c r="E234">
         <v>2</v>
       </c>
-    </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F234">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>234</v>
       </c>
@@ -8085,8 +8803,11 @@
       <c r="E235">
         <v>2</v>
       </c>
-    </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F235">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>235</v>
       </c>
@@ -8102,8 +8823,11 @@
       <c r="E236">
         <v>2</v>
       </c>
-    </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F236">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>236</v>
       </c>
@@ -8119,8 +8843,11 @@
       <c r="E237">
         <v>2</v>
       </c>
-    </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F237">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>237</v>
       </c>
@@ -8136,8 +8863,11 @@
       <c r="E238">
         <v>2</v>
       </c>
-    </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F238">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>238</v>
       </c>
@@ -8153,8 +8883,11 @@
       <c r="E239">
         <v>2</v>
       </c>
-    </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F239">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>239</v>
       </c>
@@ -8170,8 +8903,11 @@
       <c r="E240">
         <v>2</v>
       </c>
-    </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F240">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>240</v>
       </c>
@@ -8187,8 +8923,11 @@
       <c r="E241">
         <v>2</v>
       </c>
-    </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F241">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>241</v>
       </c>
@@ -8204,8 +8943,11 @@
       <c r="E242">
         <v>2</v>
       </c>
-    </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F242">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>242</v>
       </c>
@@ -8221,8 +8963,11 @@
       <c r="E243">
         <v>2</v>
       </c>
-    </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F243">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>243</v>
       </c>
@@ -8238,8 +8983,11 @@
       <c r="E244">
         <v>2</v>
       </c>
-    </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F244">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>244</v>
       </c>
@@ -8255,8 +9003,11 @@
       <c r="E245">
         <v>2</v>
       </c>
-    </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F245">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>245</v>
       </c>
@@ -8272,8 +9023,11 @@
       <c r="E246">
         <v>2</v>
       </c>
-    </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F246">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>246</v>
       </c>
@@ -8289,8 +9043,11 @@
       <c r="E247">
         <v>2</v>
       </c>
-    </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F247">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>247</v>
       </c>
@@ -8306,8 +9063,11 @@
       <c r="E248">
         <v>2</v>
       </c>
-    </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F248">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>248</v>
       </c>
@@ -8323,8 +9083,11 @@
       <c r="E249">
         <v>2</v>
       </c>
-    </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F249">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>249</v>
       </c>
@@ -8340,8 +9103,11 @@
       <c r="E250">
         <v>2</v>
       </c>
-    </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F250">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>250</v>
       </c>
@@ -8357,8 +9123,11 @@
       <c r="E251">
         <v>2</v>
       </c>
-    </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F251">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>251</v>
       </c>
@@ -8374,8 +9143,11 @@
       <c r="E252">
         <v>2</v>
       </c>
-    </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F252">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>252</v>
       </c>
@@ -8391,8 +9163,11 @@
       <c r="E253">
         <v>2</v>
       </c>
-    </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F253">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>253</v>
       </c>
@@ -8408,8 +9183,11 @@
       <c r="E254">
         <v>2</v>
       </c>
-    </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F254">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>254</v>
       </c>
@@ -8425,8 +9203,11 @@
       <c r="E255">
         <v>2</v>
       </c>
-    </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F255">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>255</v>
       </c>
@@ -8442,8 +9223,11 @@
       <c r="E256">
         <v>2</v>
       </c>
-    </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F256">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>256</v>
       </c>
@@ -8459,8 +9243,11 @@
       <c r="E257">
         <v>3</v>
       </c>
-    </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F257">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>257</v>
       </c>
@@ -8476,8 +9263,11 @@
       <c r="E258">
         <v>3</v>
       </c>
-    </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F258">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>258</v>
       </c>
@@ -8493,8 +9283,11 @@
       <c r="E259">
         <v>3</v>
       </c>
-    </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F259">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>259</v>
       </c>
@@ -8510,8 +9303,11 @@
       <c r="E260">
         <v>3</v>
       </c>
-    </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F260">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>260</v>
       </c>
@@ -8527,8 +9323,11 @@
       <c r="E261">
         <v>3</v>
       </c>
-    </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F261">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>261</v>
       </c>
@@ -8544,8 +9343,11 @@
       <c r="E262">
         <v>3</v>
       </c>
-    </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F262">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>262</v>
       </c>
@@ -8561,8 +9363,11 @@
       <c r="E263">
         <v>3</v>
       </c>
-    </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F263">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>263</v>
       </c>
@@ -8578,8 +9383,11 @@
       <c r="E264">
         <v>4</v>
       </c>
-    </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F264">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>264</v>
       </c>
@@ -8595,8 +9403,11 @@
       <c r="E265">
         <v>4</v>
       </c>
-    </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F265">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>265</v>
       </c>
@@ -8612,8 +9423,11 @@
       <c r="E266">
         <v>4</v>
       </c>
-    </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F266">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>266</v>
       </c>
@@ -8629,8 +9443,11 @@
       <c r="E267">
         <v>4</v>
       </c>
-    </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F267">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>267</v>
       </c>
@@ -8646,8 +9463,11 @@
       <c r="E268">
         <v>4</v>
       </c>
-    </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F268">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>268</v>
       </c>
@@ -8663,8 +9483,11 @@
       <c r="E269">
         <v>4</v>
       </c>
-    </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F269">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>269</v>
       </c>
@@ -8680,8 +9503,11 @@
       <c r="E270">
         <v>4</v>
       </c>
-    </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F270">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>270</v>
       </c>
@@ -8697,8 +9523,11 @@
       <c r="E271">
         <v>4</v>
       </c>
-    </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F271">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>271</v>
       </c>
@@ -8714,8 +9543,11 @@
       <c r="E272">
         <v>4</v>
       </c>
-    </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F272">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>272</v>
       </c>
@@ -8731,8 +9563,11 @@
       <c r="E273">
         <v>4</v>
       </c>
-    </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F273">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>273</v>
       </c>
@@ -8748,8 +9583,11 @@
       <c r="E274">
         <v>4</v>
       </c>
-    </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F274">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>274</v>
       </c>
@@ -8765,8 +9603,11 @@
       <c r="E275">
         <v>4</v>
       </c>
-    </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F275">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>275</v>
       </c>
@@ -8782,8 +9623,11 @@
       <c r="E276">
         <v>4</v>
       </c>
-    </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F276">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>276</v>
       </c>
@@ -8799,8 +9643,11 @@
       <c r="E277">
         <v>4</v>
       </c>
-    </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F277">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>277</v>
       </c>
@@ -8816,8 +9663,11 @@
       <c r="E278">
         <v>4</v>
       </c>
-    </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F278">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>278</v>
       </c>
@@ -8833,8 +9683,11 @@
       <c r="E279">
         <v>4</v>
       </c>
-    </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F279">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>279</v>
       </c>
@@ -8850,8 +9703,11 @@
       <c r="E280">
         <v>4</v>
       </c>
-    </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F280">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>280</v>
       </c>
@@ -8867,8 +9723,11 @@
       <c r="E281">
         <v>4</v>
       </c>
-    </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F281">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>281</v>
       </c>
@@ -8884,8 +9743,11 @@
       <c r="E282">
         <v>4</v>
       </c>
-    </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F282">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>282</v>
       </c>
@@ -8901,8 +9763,11 @@
       <c r="E283">
         <v>4</v>
       </c>
-    </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F283">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>283</v>
       </c>
@@ -8918,8 +9783,11 @@
       <c r="E284">
         <v>4</v>
       </c>
-    </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F284">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>284</v>
       </c>
@@ -8935,8 +9803,11 @@
       <c r="E285">
         <v>4</v>
       </c>
-    </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F285">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>285</v>
       </c>
@@ -8952,8 +9823,11 @@
       <c r="E286">
         <v>4</v>
       </c>
-    </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F286">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>286</v>
       </c>
@@ -8969,8 +9843,11 @@
       <c r="E287">
         <v>5</v>
       </c>
-    </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F287">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>287</v>
       </c>
@@ -8986,8 +9863,11 @@
       <c r="E288">
         <v>5</v>
       </c>
-    </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F288">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>288</v>
       </c>
@@ -9003,8 +9883,11 @@
       <c r="E289">
         <v>5</v>
       </c>
-    </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F289">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>289</v>
       </c>
@@ -9020,8 +9903,11 @@
       <c r="E290">
         <v>5</v>
       </c>
-    </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F290">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>290</v>
       </c>
@@ -9037,8 +9923,11 @@
       <c r="E291">
         <v>5</v>
       </c>
-    </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F291">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>291</v>
       </c>
@@ -9054,8 +9943,11 @@
       <c r="E292">
         <v>5</v>
       </c>
-    </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F292">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>292</v>
       </c>
@@ -9071,8 +9963,11 @@
       <c r="E293">
         <v>5</v>
       </c>
-    </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F293">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>293</v>
       </c>
@@ -9088,8 +9983,11 @@
       <c r="E294">
         <v>5</v>
       </c>
-    </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F294">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>294</v>
       </c>
@@ -9105,8 +10003,11 @@
       <c r="E295">
         <v>5</v>
       </c>
-    </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F295">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>295</v>
       </c>
@@ -9122,8 +10023,11 @@
       <c r="E296">
         <v>5</v>
       </c>
-    </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F296">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>296</v>
       </c>
@@ -9139,8 +10043,11 @@
       <c r="E297">
         <v>5</v>
       </c>
-    </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F297">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>297</v>
       </c>
@@ -9156,8 +10063,11 @@
       <c r="E298">
         <v>5</v>
       </c>
-    </row>
-    <row r="299" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F298">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>298</v>
       </c>
@@ -9173,8 +10083,11 @@
       <c r="E299">
         <v>5</v>
       </c>
-    </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F299">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>299</v>
       </c>
@@ -9190,8 +10103,11 @@
       <c r="E300">
         <v>5</v>
       </c>
-    </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F300">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>300</v>
       </c>
@@ -9207,8 +10123,11 @@
       <c r="E301">
         <v>5</v>
       </c>
-    </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F301">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>301</v>
       </c>
@@ -9224,8 +10143,11 @@
       <c r="E302">
         <v>5</v>
       </c>
-    </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F302">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>302</v>
       </c>
@@ -9241,8 +10163,11 @@
       <c r="E303">
         <v>5</v>
       </c>
-    </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F303">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>303</v>
       </c>
@@ -9258,8 +10183,11 @@
       <c r="E304">
         <v>5</v>
       </c>
-    </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F304">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>304</v>
       </c>
@@ -9275,8 +10203,11 @@
       <c r="E305">
         <v>5</v>
       </c>
-    </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F305">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>305</v>
       </c>
@@ -9292,8 +10223,11 @@
       <c r="E306">
         <v>5</v>
       </c>
-    </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F306">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>306</v>
       </c>
@@ -9309,8 +10243,11 @@
       <c r="E307">
         <v>0</v>
       </c>
-    </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F307">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>307</v>
       </c>
@@ -9326,8 +10263,11 @@
       <c r="E308">
         <v>0</v>
       </c>
-    </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F308">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="309" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>308</v>
       </c>
@@ -9343,8 +10283,11 @@
       <c r="E309">
         <v>0</v>
       </c>
-    </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F309">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>309</v>
       </c>
@@ -9360,8 +10303,11 @@
       <c r="E310">
         <v>0</v>
       </c>
-    </row>
-    <row r="311" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F310">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>310</v>
       </c>
@@ -9377,8 +10323,11 @@
       <c r="E311">
         <v>0</v>
       </c>
-    </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F311">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>311</v>
       </c>
@@ -9394,8 +10343,11 @@
       <c r="E312">
         <v>0</v>
       </c>
-    </row>
-    <row r="313" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F312">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="313" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>312</v>
       </c>
@@ -9411,8 +10363,11 @@
       <c r="E313">
         <v>0</v>
       </c>
-    </row>
-    <row r="314" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F313">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="314" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>313</v>
       </c>
@@ -9428,8 +10383,11 @@
       <c r="E314">
         <v>0</v>
       </c>
-    </row>
-    <row r="315" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F314">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="315" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>314</v>
       </c>
@@ -9445,8 +10403,11 @@
       <c r="E315">
         <v>0</v>
       </c>
-    </row>
-    <row r="316" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F315">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>315</v>
       </c>
@@ -9462,8 +10423,11 @@
       <c r="E316">
         <v>0</v>
       </c>
-    </row>
-    <row r="317" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F316">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="317" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>316</v>
       </c>
@@ -9479,8 +10443,11 @@
       <c r="E317">
         <v>0</v>
       </c>
-    </row>
-    <row r="318" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F317">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="318" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>317</v>
       </c>
@@ -9496,8 +10463,11 @@
       <c r="E318">
         <v>0</v>
       </c>
-    </row>
-    <row r="319" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F318">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="319" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>318</v>
       </c>
@@ -9513,8 +10483,11 @@
       <c r="E319">
         <v>0</v>
       </c>
-    </row>
-    <row r="320" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F319">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>319</v>
       </c>
@@ -9530,8 +10503,11 @@
       <c r="E320">
         <v>0</v>
       </c>
-    </row>
-    <row r="321" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F320">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="321" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>320</v>
       </c>
@@ -9547,8 +10523,11 @@
       <c r="E321">
         <v>0</v>
       </c>
-    </row>
-    <row r="322" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F321">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="322" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>321</v>
       </c>
@@ -9564,8 +10543,11 @@
       <c r="E322">
         <v>1</v>
       </c>
-    </row>
-    <row r="323" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F322">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="323" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>322</v>
       </c>
@@ -9581,8 +10563,11 @@
       <c r="E323">
         <v>1</v>
       </c>
-    </row>
-    <row r="324" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F323">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="324" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>323</v>
       </c>
@@ -9598,8 +10583,11 @@
       <c r="E324">
         <v>1</v>
       </c>
-    </row>
-    <row r="325" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F324">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="325" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>324</v>
       </c>
@@ -9615,8 +10603,11 @@
       <c r="E325">
         <v>2</v>
       </c>
-    </row>
-    <row r="326" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F325">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="326" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>325</v>
       </c>
@@ -9632,8 +10623,11 @@
       <c r="E326">
         <v>2</v>
       </c>
-    </row>
-    <row r="327" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F326">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="327" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>326</v>
       </c>
@@ -9649,8 +10643,11 @@
       <c r="E327">
         <v>2</v>
       </c>
-    </row>
-    <row r="328" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F327">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="328" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>327</v>
       </c>
@@ -9666,8 +10663,11 @@
       <c r="E328">
         <v>2</v>
       </c>
-    </row>
-    <row r="329" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F328">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="329" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>328</v>
       </c>
@@ -9683,8 +10683,11 @@
       <c r="E329">
         <v>3</v>
       </c>
-    </row>
-    <row r="330" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F329">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="330" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>329</v>
       </c>
@@ -9700,8 +10703,11 @@
       <c r="E330">
         <v>3</v>
       </c>
-    </row>
-    <row r="331" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F330">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="331" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>330</v>
       </c>
@@ -9717,8 +10723,11 @@
       <c r="E331">
         <v>3</v>
       </c>
-    </row>
-    <row r="332" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F331">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="332" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>331</v>
       </c>
@@ -9734,8 +10743,11 @@
       <c r="E332">
         <v>3</v>
       </c>
-    </row>
-    <row r="333" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F332">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>332</v>
       </c>
@@ -9751,8 +10763,11 @@
       <c r="E333">
         <v>3</v>
       </c>
-    </row>
-    <row r="334" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F333">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="334" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>333</v>
       </c>
@@ -9768,8 +10783,11 @@
       <c r="E334">
         <v>3</v>
       </c>
-    </row>
-    <row r="335" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F334">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="335" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>334</v>
       </c>
@@ -9785,8 +10803,11 @@
       <c r="E335">
         <v>4</v>
       </c>
-    </row>
-    <row r="336" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F335">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="336" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>335</v>
       </c>
@@ -9802,8 +10823,11 @@
       <c r="E336">
         <v>4</v>
       </c>
-    </row>
-    <row r="337" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F336">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="337" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>336</v>
       </c>
@@ -9819,8 +10843,11 @@
       <c r="E337">
         <v>4</v>
       </c>
-    </row>
-    <row r="338" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F337">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="338" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>337</v>
       </c>
@@ -9836,8 +10863,11 @@
       <c r="E338">
         <v>4</v>
       </c>
-    </row>
-    <row r="339" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F338">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="339" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>338</v>
       </c>
@@ -9853,8 +10883,11 @@
       <c r="E339">
         <v>5</v>
       </c>
-    </row>
-    <row r="340" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F339">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="340" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>339</v>
       </c>
@@ -9870,8 +10903,11 @@
       <c r="E340">
         <v>5</v>
       </c>
-    </row>
-    <row r="341" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F340">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="341" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>340</v>
       </c>
@@ -9887,8 +10923,11 @@
       <c r="E341">
         <v>5</v>
       </c>
-    </row>
-    <row r="342" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F341">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="342" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>341</v>
       </c>
@@ -9904,8 +10943,11 @@
       <c r="E342">
         <v>5</v>
       </c>
-    </row>
-    <row r="343" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F342">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>342</v>
       </c>
@@ -9921,8 +10963,11 @@
       <c r="E343">
         <v>5</v>
       </c>
-    </row>
-    <row r="344" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F343">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="344" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>343</v>
       </c>
@@ -9938,8 +10983,11 @@
       <c r="E344">
         <v>5</v>
       </c>
-    </row>
-    <row r="345" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F344">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="345" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>344</v>
       </c>
@@ -9955,8 +11003,11 @@
       <c r="E345">
         <v>5</v>
       </c>
-    </row>
-    <row r="346" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F345">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="346" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>345</v>
       </c>
@@ -9972,8 +11023,11 @@
       <c r="E346">
         <v>5</v>
       </c>
-    </row>
-    <row r="347" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F346">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="347" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>346</v>
       </c>
@@ -9989,8 +11043,11 @@
       <c r="E347">
         <v>5</v>
       </c>
-    </row>
-    <row r="348" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F347">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>347</v>
       </c>
@@ -10006,8 +11063,11 @@
       <c r="E348">
         <v>5</v>
       </c>
-    </row>
-    <row r="349" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F348">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="349" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>348</v>
       </c>
@@ -10023,8 +11083,11 @@
       <c r="E349">
         <v>5</v>
       </c>
-    </row>
-    <row r="350" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F349">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="350" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>349</v>
       </c>
@@ -10040,8 +11103,11 @@
       <c r="E350">
         <v>5</v>
       </c>
-    </row>
-    <row r="351" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F350">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="351" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>350</v>
       </c>
@@ -10057,8 +11123,11 @@
       <c r="E351">
         <v>5</v>
       </c>
-    </row>
-    <row r="352" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F351">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="352" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>351</v>
       </c>
@@ -10074,8 +11143,11 @@
       <c r="E352">
         <v>5</v>
       </c>
-    </row>
-    <row r="353" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F352">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="353" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>352</v>
       </c>
@@ -10091,8 +11163,11 @@
       <c r="E353">
         <v>5</v>
       </c>
-    </row>
-    <row r="354" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F353">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="354" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>353</v>
       </c>
@@ -10108,8 +11183,11 @@
       <c r="E354">
         <v>5</v>
       </c>
-    </row>
-    <row r="355" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F354">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="355" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>354</v>
       </c>
@@ -10125,8 +11203,11 @@
       <c r="E355">
         <v>5</v>
       </c>
-    </row>
-    <row r="356" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F355">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="356" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>355</v>
       </c>
@@ -10142,8 +11223,11 @@
       <c r="E356">
         <v>5</v>
       </c>
-    </row>
-    <row r="357" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F356">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="357" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>356</v>
       </c>
@@ -10159,8 +11243,11 @@
       <c r="E357">
         <v>5</v>
       </c>
-    </row>
-    <row r="358" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F357">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="358" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>357</v>
       </c>
@@ -10176,8 +11263,11 @@
       <c r="E358">
         <v>5</v>
       </c>
-    </row>
-    <row r="359" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F358">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="359" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>358</v>
       </c>
@@ -10193,8 +11283,11 @@
       <c r="E359">
         <v>0</v>
       </c>
-    </row>
-    <row r="360" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F359">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="360" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>359</v>
       </c>
@@ -10210,8 +11303,11 @@
       <c r="E360">
         <v>0</v>
       </c>
-    </row>
-    <row r="361" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F360">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="361" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>360</v>
       </c>
@@ -10227,8 +11323,11 @@
       <c r="E361">
         <v>2</v>
       </c>
-    </row>
-    <row r="362" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F361">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="362" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>361</v>
       </c>
@@ -10244,8 +11343,11 @@
       <c r="E362">
         <v>2</v>
       </c>
-    </row>
-    <row r="363" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F362">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="363" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>362</v>
       </c>
@@ -10261,8 +11363,11 @@
       <c r="E363">
         <v>2</v>
       </c>
-    </row>
-    <row r="364" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F363">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="364" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>363</v>
       </c>
@@ -10278,8 +11383,11 @@
       <c r="E364">
         <v>2</v>
       </c>
-    </row>
-    <row r="365" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F364">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="365" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>364</v>
       </c>
@@ -10295,8 +11403,11 @@
       <c r="E365">
         <v>2</v>
       </c>
-    </row>
-    <row r="366" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F365">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="366" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>365</v>
       </c>
@@ -10312,8 +11423,11 @@
       <c r="E366">
         <v>4</v>
       </c>
-    </row>
-    <row r="367" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F366">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>366</v>
       </c>
@@ -10329,8 +11443,11 @@
       <c r="E367">
         <v>4</v>
       </c>
-    </row>
-    <row r="368" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F367">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="368" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>367</v>
       </c>
@@ -10346,8 +11463,11 @@
       <c r="E368">
         <v>4</v>
       </c>
-    </row>
-    <row r="369" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F368">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="369" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>368</v>
       </c>
@@ -10363,8 +11483,11 @@
       <c r="E369">
         <v>5</v>
       </c>
-    </row>
-    <row r="370" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F369">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>369</v>
       </c>
@@ -10380,8 +11503,11 @@
       <c r="E370">
         <v>5</v>
       </c>
-    </row>
-    <row r="371" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F370">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="371" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>370</v>
       </c>
@@ -10397,8 +11523,11 @@
       <c r="E371">
         <v>5</v>
       </c>
-    </row>
-    <row r="372" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F371">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="372" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>371</v>
       </c>
@@ -10414,8 +11543,11 @@
       <c r="E372">
         <v>0</v>
       </c>
-    </row>
-    <row r="373" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F372">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="373" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>372</v>
       </c>
@@ -10431,8 +11563,11 @@
       <c r="E373">
         <v>0</v>
       </c>
-    </row>
-    <row r="374" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F373">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="374" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>373</v>
       </c>
@@ -10448,8 +11583,11 @@
       <c r="E374">
         <v>1</v>
       </c>
-    </row>
-    <row r="375" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F374">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="375" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>374</v>
       </c>
@@ -10465,8 +11603,11 @@
       <c r="E375">
         <v>5</v>
       </c>
-    </row>
-    <row r="376" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F375">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="376" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>375</v>
       </c>
@@ -10482,8 +11623,11 @@
       <c r="E376">
         <v>5</v>
       </c>
-    </row>
-    <row r="377" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F376">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="377" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>376</v>
       </c>
@@ -10499,8 +11643,11 @@
       <c r="E377">
         <v>2</v>
       </c>
-    </row>
-    <row r="378" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F377">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="378" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>377</v>
       </c>
@@ -10516,8 +11663,11 @@
       <c r="E378">
         <v>2</v>
       </c>
-    </row>
-    <row r="379" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F378">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>378</v>
       </c>
@@ -10533,8 +11683,11 @@
       <c r="E379">
         <v>3</v>
       </c>
-    </row>
-    <row r="380" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F379">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="380" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>379</v>
       </c>
@@ -10550,8 +11703,11 @@
       <c r="E380">
         <v>0</v>
       </c>
-    </row>
-    <row r="381" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F380">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="381" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>380</v>
       </c>
@@ -10567,8 +11723,11 @@
       <c r="E381">
         <v>5</v>
       </c>
-    </row>
-    <row r="382" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F381">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="382" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>381</v>
       </c>
@@ -10584,8 +11743,11 @@
       <c r="E382">
         <v>2</v>
       </c>
-    </row>
-    <row r="383" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F382">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="383" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>382</v>
       </c>
@@ -10601,8 +11763,11 @@
       <c r="E383">
         <v>2</v>
       </c>
-    </row>
-    <row r="384" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F383">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="384" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>383</v>
       </c>
@@ -10618,8 +11783,11 @@
       <c r="E384">
         <v>2</v>
       </c>
-    </row>
-    <row r="385" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F384">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="385" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>384</v>
       </c>
@@ -10635,8 +11803,11 @@
       <c r="E385">
         <v>2</v>
       </c>
-    </row>
-    <row r="386" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F385">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="386" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>385</v>
       </c>
@@ -10652,8 +11823,11 @@
       <c r="E386">
         <v>2</v>
       </c>
-    </row>
-    <row r="387" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F386">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="387" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>386</v>
       </c>
@@ -10669,8 +11843,11 @@
       <c r="E387">
         <v>2</v>
       </c>
-    </row>
-    <row r="388" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F387">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="388" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>387</v>
       </c>
@@ -10686,8 +11863,11 @@
       <c r="E388">
         <v>3</v>
       </c>
-    </row>
-    <row r="389" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F388">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="389" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>388</v>
       </c>
@@ -10703,8 +11883,11 @@
       <c r="E389">
         <v>0</v>
       </c>
-    </row>
-    <row r="390" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F389">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="390" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>389</v>
       </c>
@@ -10720,8 +11903,11 @@
       <c r="E390">
         <v>2</v>
       </c>
-    </row>
-    <row r="391" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F390">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="391" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>390</v>
       </c>
@@ -10737,8 +11923,11 @@
       <c r="E391">
         <v>3</v>
       </c>
-    </row>
-    <row r="392" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F391">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="392" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>391</v>
       </c>
@@ -10754,8 +11943,11 @@
       <c r="E392">
         <v>4</v>
       </c>
-    </row>
-    <row r="393" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F392">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="393" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>392</v>
       </c>
@@ -10771,8 +11963,11 @@
       <c r="E393">
         <v>1</v>
       </c>
-    </row>
-    <row r="394" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F393">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="394" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>393</v>
       </c>
@@ -10788,8 +11983,11 @@
       <c r="E394">
         <v>5</v>
       </c>
-    </row>
-    <row r="395" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F394">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="395" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>394</v>
       </c>
@@ -10805,8 +12003,11 @@
       <c r="E395">
         <v>2</v>
       </c>
-    </row>
-    <row r="396" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F395">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="396" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>395</v>
       </c>
@@ -10822,8 +12023,11 @@
       <c r="E396">
         <v>0</v>
       </c>
-    </row>
-    <row r="397" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F396">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="397" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>396</v>
       </c>
@@ -10839,8 +12043,11 @@
       <c r="E397">
         <v>3</v>
       </c>
-    </row>
-    <row r="398" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F397">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="398" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>397</v>
       </c>
@@ -10856,8 +12063,11 @@
       <c r="E398">
         <v>4</v>
       </c>
-    </row>
-    <row r="399" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F398">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="399" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>398</v>
       </c>
@@ -10873,8 +12083,11 @@
       <c r="E399">
         <v>2</v>
       </c>
-    </row>
-    <row r="400" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F399">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="400" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>399</v>
       </c>
@@ -10890,8 +12103,11 @@
       <c r="E400">
         <v>4</v>
       </c>
-    </row>
-    <row r="401" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F400">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="401" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>400</v>
       </c>
@@ -10907,8 +12123,11 @@
       <c r="E401">
         <v>4</v>
       </c>
-    </row>
-    <row r="402" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F401">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="402" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>401</v>
       </c>
@@ -10924,8 +12143,11 @@
       <c r="E402">
         <v>2</v>
       </c>
-    </row>
-    <row r="403" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F402">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="403" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>402</v>
       </c>
@@ -10941,8 +12163,11 @@
       <c r="E403">
         <v>3</v>
       </c>
-    </row>
-    <row r="404" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F403">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="404" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>403</v>
       </c>
@@ -10958,8 +12183,11 @@
       <c r="E404">
         <v>4</v>
       </c>
-    </row>
-    <row r="405" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F404">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>404</v>
       </c>
@@ -10975,8 +12203,11 @@
       <c r="E405">
         <v>3</v>
       </c>
-    </row>
-    <row r="406" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F405">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="406" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>405</v>
       </c>
@@ -10992,8 +12223,11 @@
       <c r="E406">
         <v>2</v>
       </c>
-    </row>
-    <row r="407" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F406">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="407" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>406</v>
       </c>
@@ -11009,8 +12243,11 @@
       <c r="E407">
         <v>2</v>
       </c>
-    </row>
-    <row r="408" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F407">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="408" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>407</v>
       </c>
@@ -11026,8 +12263,11 @@
       <c r="E408">
         <v>2</v>
       </c>
-    </row>
-    <row r="409" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F408">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="409" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>408</v>
       </c>
@@ -11043,8 +12283,11 @@
       <c r="E409">
         <v>4</v>
       </c>
-    </row>
-    <row r="410" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F409">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="410" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>409</v>
       </c>
@@ -11060,8 +12303,11 @@
       <c r="E410">
         <v>2</v>
       </c>
-    </row>
-    <row r="411" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F410">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="411" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>410</v>
       </c>
@@ -11077,8 +12323,11 @@
       <c r="E411">
         <v>1</v>
       </c>
-    </row>
-    <row r="412" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F411">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="412" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>411</v>
       </c>
@@ -11094,8 +12343,11 @@
       <c r="E412">
         <v>0</v>
       </c>
-    </row>
-    <row r="413" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F412">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="413" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>412</v>
       </c>
@@ -11111,8 +12363,11 @@
       <c r="E413">
         <v>5</v>
       </c>
-    </row>
-    <row r="414" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F413">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="414" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>413</v>
       </c>
@@ -11128,8 +12383,11 @@
       <c r="E414">
         <v>4</v>
       </c>
-    </row>
-    <row r="415" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F414">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="415" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>414</v>
       </c>
@@ -11145,8 +12403,11 @@
       <c r="E415">
         <v>4</v>
       </c>
-    </row>
-    <row r="416" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F415">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="416" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>415</v>
       </c>
@@ -11162,8 +12423,11 @@
       <c r="E416">
         <v>4</v>
       </c>
-    </row>
-    <row r="417" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F416">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="417" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>416</v>
       </c>
@@ -11179,8 +12443,11 @@
       <c r="E417">
         <v>4</v>
       </c>
-    </row>
-    <row r="418" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F417">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="418" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>417</v>
       </c>
@@ -11196,8 +12463,11 @@
       <c r="E418">
         <v>5</v>
       </c>
-    </row>
-    <row r="419" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F418">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="419" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>418</v>
       </c>
@@ -11213,8 +12483,11 @@
       <c r="E419">
         <v>0</v>
       </c>
-    </row>
-    <row r="420" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F419">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="420" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>419</v>
       </c>
@@ -11230,8 +12503,11 @@
       <c r="E420">
         <v>4</v>
       </c>
-    </row>
-    <row r="421" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F420">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="421" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>420</v>
       </c>
@@ -11247,8 +12523,11 @@
       <c r="E421">
         <v>2</v>
       </c>
-    </row>
-    <row r="422" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F421">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="422" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>421</v>
       </c>
@@ -11264,8 +12543,11 @@
       <c r="E422">
         <v>3</v>
       </c>
-    </row>
-    <row r="423" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F422">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="423" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>422</v>
       </c>
@@ -11281,8 +12563,11 @@
       <c r="E423">
         <v>3</v>
       </c>
-    </row>
-    <row r="424" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F423">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="424" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>423</v>
       </c>
@@ -11298,8 +12583,11 @@
       <c r="E424">
         <v>0</v>
       </c>
-    </row>
-    <row r="425" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F424">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="425" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>424</v>
       </c>
@@ -11315,8 +12603,11 @@
       <c r="E425">
         <v>2</v>
       </c>
-    </row>
-    <row r="426" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F425">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="426" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>425</v>
       </c>
@@ -11332,8 +12623,11 @@
       <c r="E426">
         <v>1</v>
       </c>
-    </row>
-    <row r="427" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F426">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="427" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>426</v>
       </c>
@@ -11349,8 +12643,11 @@
       <c r="E427">
         <v>2</v>
       </c>
-    </row>
-    <row r="428" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F427">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="428" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>427</v>
       </c>
@@ -11366,8 +12663,11 @@
       <c r="E428">
         <v>2</v>
       </c>
-    </row>
-    <row r="429" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F428">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="429" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>428</v>
       </c>
@@ -11383,8 +12683,11 @@
       <c r="E429">
         <v>4</v>
       </c>
-    </row>
-    <row r="430" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F429">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="430" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>429</v>
       </c>
@@ -11400,8 +12703,11 @@
       <c r="E430">
         <v>2</v>
       </c>
-    </row>
-    <row r="431" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F430">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="431" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>430</v>
       </c>
@@ -11417,8 +12723,11 @@
       <c r="E431">
         <v>4</v>
       </c>
-    </row>
-    <row r="432" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F431">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="432" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>431</v>
       </c>
@@ -11434,8 +12743,11 @@
       <c r="E432">
         <v>2</v>
       </c>
-    </row>
-    <row r="433" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F432">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="433" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>432</v>
       </c>
@@ -11451,8 +12763,11 @@
       <c r="E433">
         <v>0</v>
       </c>
-    </row>
-    <row r="434" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F433">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="434" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>433</v>
       </c>
@@ -11468,8 +12783,11 @@
       <c r="E434">
         <v>2</v>
       </c>
-    </row>
-    <row r="435" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F434">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="435" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>434</v>
       </c>
@@ -11485,8 +12803,11 @@
       <c r="E435">
         <v>2</v>
       </c>
-    </row>
-    <row r="436" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F435">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="436" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>435</v>
       </c>
@@ -11502,8 +12823,11 @@
       <c r="E436">
         <v>4</v>
       </c>
-    </row>
-    <row r="437" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F436">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="437" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>436</v>
       </c>
@@ -11519,8 +12843,11 @@
       <c r="E437">
         <v>3</v>
       </c>
-    </row>
-    <row r="438" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F437">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="438" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>437</v>
       </c>
@@ -11536,8 +12863,11 @@
       <c r="E438">
         <v>1</v>
       </c>
-    </row>
-    <row r="439" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F438">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="439" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>438</v>
       </c>
@@ -11553,8 +12883,11 @@
       <c r="E439">
         <v>0</v>
       </c>
-    </row>
-    <row r="440" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F439">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="440" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>439</v>
       </c>
@@ -11570,8 +12903,11 @@
       <c r="E440">
         <v>0</v>
       </c>
-    </row>
-    <row r="441" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F440">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="441" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>440</v>
       </c>
@@ -11587,8 +12923,11 @@
       <c r="E441">
         <v>0</v>
       </c>
-    </row>
-    <row r="442" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F441">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="442" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>441</v>
       </c>
@@ -11604,8 +12943,11 @@
       <c r="E442">
         <v>0</v>
       </c>
-    </row>
-    <row r="443" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F442">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="443" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>442</v>
       </c>
@@ -11621,8 +12963,11 @@
       <c r="E443">
         <v>1</v>
       </c>
-    </row>
-    <row r="444" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F443">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="444" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>443</v>
       </c>
@@ -11638,8 +12983,11 @@
       <c r="E444">
         <v>1</v>
       </c>
-    </row>
-    <row r="445" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F444">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="445" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>444</v>
       </c>
@@ -11655,8 +13003,11 @@
       <c r="E445">
         <v>1</v>
       </c>
-    </row>
-    <row r="446" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F445">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="446" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>445</v>
       </c>
@@ -11672,8 +13023,11 @@
       <c r="E446">
         <v>2</v>
       </c>
-    </row>
-    <row r="447" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F446">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="447" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>446</v>
       </c>
@@ -11689,8 +13043,11 @@
       <c r="E447">
         <v>2</v>
       </c>
-    </row>
-    <row r="448" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F447">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="448" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>447</v>
       </c>
@@ -11706,8 +13063,11 @@
       <c r="E448">
         <v>2</v>
       </c>
-    </row>
-    <row r="449" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F448">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="449" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>448</v>
       </c>
@@ -11723,8 +13083,11 @@
       <c r="E449">
         <v>2</v>
       </c>
-    </row>
-    <row r="450" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F449">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="450" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>449</v>
       </c>
@@ -11740,8 +13103,11 @@
       <c r="E450">
         <v>2</v>
       </c>
-    </row>
-    <row r="451" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F450">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="451" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>450</v>
       </c>
@@ -11757,8 +13123,11 @@
       <c r="E451">
         <v>2</v>
       </c>
-    </row>
-    <row r="452" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F451">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="452" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>451</v>
       </c>
@@ -11774,8 +13143,11 @@
       <c r="E452">
         <v>2</v>
       </c>
-    </row>
-    <row r="453" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F452">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="453" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>452</v>
       </c>
@@ -11791,8 +13163,11 @@
       <c r="E453">
         <v>2</v>
       </c>
-    </row>
-    <row r="454" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F453">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="454" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>453</v>
       </c>
@@ -11808,8 +13183,11 @@
       <c r="E454">
         <v>2</v>
       </c>
-    </row>
-    <row r="455" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F454">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="455" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>454</v>
       </c>
@@ -11825,8 +13203,11 @@
       <c r="E455">
         <v>2</v>
       </c>
-    </row>
-    <row r="456" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F455">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="456" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>455</v>
       </c>
@@ -11842,8 +13223,11 @@
       <c r="E456">
         <v>3</v>
       </c>
-    </row>
-    <row r="457" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F456">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="457" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>456</v>
       </c>
@@ -11859,8 +13243,11 @@
       <c r="E457">
         <v>4</v>
       </c>
-    </row>
-    <row r="458" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F457">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="458" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>457</v>
       </c>
@@ -11876,8 +13263,11 @@
       <c r="E458">
         <v>4</v>
       </c>
-    </row>
-    <row r="459" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F458">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="459" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>458</v>
       </c>
@@ -11893,8 +13283,11 @@
       <c r="E459">
         <v>4</v>
       </c>
-    </row>
-    <row r="460" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F459">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="460" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>459</v>
       </c>
@@ -11910,8 +13303,11 @@
       <c r="E460">
         <v>4</v>
       </c>
-    </row>
-    <row r="461" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F460">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="461" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>460</v>
       </c>
@@ -11927,8 +13323,11 @@
       <c r="E461">
         <v>5</v>
       </c>
-    </row>
-    <row r="462" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F461">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="462" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>461</v>
       </c>
@@ -11944,8 +13343,11 @@
       <c r="E462">
         <v>5</v>
       </c>
-    </row>
-    <row r="463" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F462">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="463" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>462</v>
       </c>
@@ -11961,8 +13363,11 @@
       <c r="E463">
         <v>5</v>
       </c>
-    </row>
-    <row r="464" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F463">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="464" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>463</v>
       </c>
@@ -11978,8 +13383,11 @@
       <c r="E464">
         <v>0</v>
       </c>
-    </row>
-    <row r="465" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F464">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="465" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>464</v>
       </c>
@@ -11995,8 +13403,11 @@
       <c r="E465">
         <v>0</v>
       </c>
-    </row>
-    <row r="466" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F465">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="466" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>465</v>
       </c>
@@ -12012,8 +13423,11 @@
       <c r="E466">
         <v>0</v>
       </c>
-    </row>
-    <row r="467" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F466">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="467" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>466</v>
       </c>
@@ -12029,8 +13443,11 @@
       <c r="E467">
         <v>0</v>
       </c>
-    </row>
-    <row r="468" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F467">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="468" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>467</v>
       </c>
@@ -12046,8 +13463,11 @@
       <c r="E468">
         <v>0</v>
       </c>
-    </row>
-    <row r="469" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F468">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="469" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>468</v>
       </c>
@@ -12063,8 +13483,11 @@
       <c r="E469">
         <v>1</v>
       </c>
-    </row>
-    <row r="470" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F469">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="470" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>469</v>
       </c>
@@ -12080,8 +13503,11 @@
       <c r="E470">
         <v>1</v>
       </c>
-    </row>
-    <row r="471" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F470">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="471" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>470</v>
       </c>
@@ -12097,8 +13523,11 @@
       <c r="E471">
         <v>1</v>
       </c>
-    </row>
-    <row r="472" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F471">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="472" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>471</v>
       </c>
@@ -12114,8 +13543,11 @@
       <c r="E472">
         <v>1</v>
       </c>
-    </row>
-    <row r="473" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F472">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="473" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>472</v>
       </c>
@@ -12131,8 +13563,11 @@
       <c r="E473">
         <v>4</v>
       </c>
-    </row>
-    <row r="474" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F473">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="474" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>473</v>
       </c>
@@ -12148,8 +13583,11 @@
       <c r="E474">
         <v>5</v>
       </c>
-    </row>
-    <row r="475" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F474">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="475" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>474</v>
       </c>
@@ -12165,8 +13603,11 @@
       <c r="E475">
         <v>5</v>
       </c>
-    </row>
-    <row r="476" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F475">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="476" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>475</v>
       </c>
@@ -12182,8 +13623,11 @@
       <c r="E476">
         <v>0</v>
       </c>
-    </row>
-    <row r="477" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F476">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="477" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>476</v>
       </c>
@@ -12199,8 +13643,11 @@
       <c r="E477">
         <v>0</v>
       </c>
-    </row>
-    <row r="478" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F477">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="478" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>477</v>
       </c>
@@ -12216,8 +13663,11 @@
       <c r="E478">
         <v>2</v>
       </c>
-    </row>
-    <row r="479" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F478">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="479" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>478</v>
       </c>
@@ -12233,8 +13683,11 @@
       <c r="E479">
         <v>2</v>
       </c>
-    </row>
-    <row r="480" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F479">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="480" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>479</v>
       </c>
@@ -12250,8 +13703,11 @@
       <c r="E480">
         <v>5</v>
       </c>
-    </row>
-    <row r="481" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F480">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="481" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>480</v>
       </c>
@@ -12267,8 +13723,11 @@
       <c r="E481">
         <v>0</v>
       </c>
-    </row>
-    <row r="482" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F481">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="482" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>481</v>
       </c>
@@ -12284,8 +13743,11 @@
       <c r="E482">
         <v>2</v>
       </c>
-    </row>
-    <row r="483" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F482">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="483" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>482</v>
       </c>
@@ -12301,8 +13763,11 @@
       <c r="E483">
         <v>2</v>
       </c>
-    </row>
-    <row r="484" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F483">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="484" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>483</v>
       </c>
@@ -12318,8 +13783,11 @@
       <c r="E484">
         <v>5</v>
       </c>
-    </row>
-    <row r="485" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F484">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="485" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
         <v>484</v>
       </c>
@@ -12335,8 +13803,11 @@
       <c r="E485">
         <v>2</v>
       </c>
-    </row>
-    <row r="486" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F485">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="486" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>485</v>
       </c>
@@ -12352,8 +13823,11 @@
       <c r="E486">
         <v>0</v>
       </c>
-    </row>
-    <row r="487" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F486">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="487" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>486</v>
       </c>
@@ -12369,8 +13843,11 @@
       <c r="E487">
         <v>5</v>
       </c>
-    </row>
-    <row r="488" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F487">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="488" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>487</v>
       </c>
@@ -12386,8 +13863,11 @@
       <c r="E488">
         <v>3</v>
       </c>
-    </row>
-    <row r="489" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F488">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="489" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>488</v>
       </c>
@@ -12403,8 +13883,11 @@
       <c r="E489">
         <v>0</v>
       </c>
-    </row>
-    <row r="490" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F489">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="490" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>489</v>
       </c>
@@ -12420,8 +13903,11 @@
       <c r="E490">
         <v>2</v>
       </c>
-    </row>
-    <row r="491" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F490">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="491" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>490</v>
       </c>
@@ -12437,8 +13923,11 @@
       <c r="E491">
         <v>5</v>
       </c>
-    </row>
-    <row r="492" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F491">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="492" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>491</v>
       </c>
@@ -12454,8 +13943,11 @@
       <c r="E492">
         <v>0</v>
       </c>
-    </row>
-    <row r="493" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F492">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="493" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>492</v>
       </c>
@@ -12471,8 +13963,11 @@
       <c r="E493">
         <v>4</v>
       </c>
-    </row>
-    <row r="494" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F493">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="494" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>493</v>
       </c>
@@ -12488,8 +13983,11 @@
       <c r="E494">
         <v>4</v>
       </c>
-    </row>
-    <row r="495" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F494">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="495" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>494</v>
       </c>
@@ -12505,8 +14003,11 @@
       <c r="E495">
         <v>2</v>
       </c>
-    </row>
-    <row r="496" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F495">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="496" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>495</v>
       </c>
@@ -12522,8 +14023,11 @@
       <c r="E496">
         <v>2</v>
       </c>
-    </row>
-    <row r="497" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F496">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="497" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>496</v>
       </c>
@@ -12539,8 +14043,11 @@
       <c r="E497">
         <v>2</v>
       </c>
-    </row>
-    <row r="498" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F497">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="498" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>497</v>
       </c>
@@ -12556,8 +14063,11 @@
       <c r="E498">
         <v>1</v>
       </c>
-    </row>
-    <row r="499" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F498">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="499" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>498</v>
       </c>
@@ -12573,8 +14083,11 @@
       <c r="E499">
         <v>0</v>
       </c>
-    </row>
-    <row r="500" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F499">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="500" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>499</v>
       </c>
@@ -12590,8 +14103,11 @@
       <c r="E500">
         <v>2</v>
       </c>
-    </row>
-    <row r="501" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F500">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="501" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>500</v>
       </c>
@@ -12607,8 +14123,11 @@
       <c r="E501">
         <v>5</v>
       </c>
-    </row>
-    <row r="502" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F501">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="502" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>501</v>
       </c>
@@ -12624,8 +14143,11 @@
       <c r="E502">
         <v>5</v>
       </c>
-    </row>
-    <row r="503" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F502">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="503" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>502</v>
       </c>
@@ -12641,8 +14163,11 @@
       <c r="E503">
         <v>2</v>
       </c>
-    </row>
-    <row r="504" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F503">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="504" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
         <v>503</v>
       </c>
@@ -12658,8 +14183,11 @@
       <c r="E504">
         <v>3</v>
       </c>
-    </row>
-    <row r="505" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F504">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="505" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
         <v>504</v>
       </c>
@@ -12675,8 +14203,11 @@
       <c r="E505">
         <v>2</v>
       </c>
-    </row>
-    <row r="506" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F505">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="506" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
         <v>505</v>
       </c>
@@ -12692,8 +14223,11 @@
       <c r="E506">
         <v>1</v>
       </c>
-    </row>
-    <row r="507" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F506">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="507" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
         <v>506</v>
       </c>
@@ -12709,8 +14243,11 @@
       <c r="E507">
         <v>0</v>
       </c>
-    </row>
-    <row r="508" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F507">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="508" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>507</v>
       </c>
@@ -12726,8 +14263,11 @@
       <c r="E508">
         <v>0</v>
       </c>
-    </row>
-    <row r="509" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F508">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="509" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
         <v>508</v>
       </c>
@@ -12743,8 +14283,11 @@
       <c r="E509">
         <v>0</v>
       </c>
-    </row>
-    <row r="510" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F509">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="510" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
         <v>509</v>
       </c>
@@ -12760,8 +14303,11 @@
       <c r="E510">
         <v>1</v>
       </c>
-    </row>
-    <row r="511" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F510">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="511" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
         <v>510</v>
       </c>
@@ -12777,8 +14323,11 @@
       <c r="E511">
         <v>2</v>
       </c>
-    </row>
-    <row r="512" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F511">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="512" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
         <v>511</v>
       </c>
@@ -12794,8 +14343,11 @@
       <c r="E512">
         <v>4</v>
       </c>
-    </row>
-    <row r="513" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F512">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="513" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
         <v>512</v>
       </c>
@@ -12811,8 +14363,11 @@
       <c r="E513">
         <v>0</v>
       </c>
-    </row>
-    <row r="514" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F513">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="514" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
         <v>513</v>
       </c>
@@ -12828,8 +14383,11 @@
       <c r="E514">
         <v>4</v>
       </c>
-    </row>
-    <row r="515" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F514">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="515" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
         <v>514</v>
       </c>
@@ -12845,8 +14403,11 @@
       <c r="E515">
         <v>3</v>
       </c>
-    </row>
-    <row r="516" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F515">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="516" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>515</v>
       </c>
@@ -12862,8 +14423,11 @@
       <c r="E516">
         <v>5</v>
       </c>
-    </row>
-    <row r="517" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F516">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="517" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
         <v>516</v>
       </c>
@@ -12879,8 +14443,11 @@
       <c r="E517">
         <v>2</v>
       </c>
-    </row>
-    <row r="518" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F517">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="518" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
         <v>517</v>
       </c>
@@ -12896,8 +14463,11 @@
       <c r="E518">
         <v>4</v>
       </c>
-    </row>
-    <row r="519" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F518">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="519" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
         <v>518</v>
       </c>
@@ -12913,8 +14483,11 @@
       <c r="E519">
         <v>2</v>
       </c>
-    </row>
-    <row r="520" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F519">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="520" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
         <v>519</v>
       </c>
@@ -12930,8 +14503,11 @@
       <c r="E520">
         <v>2</v>
       </c>
-    </row>
-    <row r="521" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F520">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="521" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
         <v>520</v>
       </c>
@@ -12947,8 +14523,11 @@
       <c r="E521">
         <v>2</v>
       </c>
-    </row>
-    <row r="522" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F521">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="522" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
         <v>521</v>
       </c>
@@ -12964,8 +14543,11 @@
       <c r="E522">
         <v>3</v>
       </c>
-    </row>
-    <row r="523" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F522">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="523" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
         <v>522</v>
       </c>
@@ -12981,8 +14563,11 @@
       <c r="E523">
         <v>5</v>
       </c>
-    </row>
-    <row r="524" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F523">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="524" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
         <v>523</v>
       </c>
@@ -12998,8 +14583,11 @@
       <c r="E524">
         <v>0</v>
       </c>
-    </row>
-    <row r="525" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F524">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="525" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
         <v>524</v>
       </c>
@@ -13015,8 +14603,11 @@
       <c r="E525">
         <v>4</v>
       </c>
-    </row>
-    <row r="526" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F525">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="526" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
         <v>525</v>
       </c>
@@ -13032,8 +14623,11 @@
       <c r="E526">
         <v>2</v>
       </c>
-    </row>
-    <row r="527" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F526">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="527" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
         <v>526</v>
       </c>
@@ -13049,8 +14643,11 @@
       <c r="E527">
         <v>2</v>
       </c>
-    </row>
-    <row r="528" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F527">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="528" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
         <v>527</v>
       </c>
@@ -13066,8 +14663,11 @@
       <c r="E528">
         <v>5</v>
       </c>
-    </row>
-    <row r="529" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F528">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="529" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
         <v>528</v>
       </c>
@@ -13083,8 +14683,11 @@
       <c r="E529">
         <v>0</v>
       </c>
-    </row>
-    <row r="530" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F529">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="530" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
         <v>529</v>
       </c>
@@ -13100,8 +14703,11 @@
       <c r="E530">
         <v>0</v>
       </c>
-    </row>
-    <row r="531" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F530">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="531" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
         <v>530</v>
       </c>
@@ -13117,8 +14723,11 @@
       <c r="E531">
         <v>5</v>
       </c>
-    </row>
-    <row r="532" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F531">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="532" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
         <v>531</v>
       </c>
@@ -13134,8 +14743,11 @@
       <c r="E532">
         <v>3</v>
       </c>
-    </row>
-    <row r="533" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F532">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="533" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
         <v>532</v>
       </c>
@@ -13151,8 +14763,11 @@
       <c r="E533">
         <v>1</v>
       </c>
-    </row>
-    <row r="534" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F533">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="534" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
         <v>533</v>
       </c>
@@ -13168,8 +14783,11 @@
       <c r="E534">
         <v>0</v>
       </c>
-    </row>
-    <row r="535" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F534">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="535" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
         <v>534</v>
       </c>
@@ -13185,8 +14803,11 @@
       <c r="E535">
         <v>1</v>
       </c>
-    </row>
-    <row r="536" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F535">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="536" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
         <v>535</v>
       </c>
@@ -13202,8 +14823,11 @@
       <c r="E536">
         <v>4</v>
       </c>
-    </row>
-    <row r="537" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F536">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="537" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
         <v>536</v>
       </c>
@@ -13219,8 +14843,11 @@
       <c r="E537">
         <v>3</v>
       </c>
-    </row>
-    <row r="538" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F537">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="538" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
         <v>537</v>
       </c>
@@ -13236,8 +14863,11 @@
       <c r="E538">
         <v>0</v>
       </c>
-    </row>
-    <row r="539" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F538">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="539" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
         <v>538</v>
       </c>
@@ -13253,8 +14883,11 @@
       <c r="E539">
         <v>5</v>
       </c>
-    </row>
-    <row r="540" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F539">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="540" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
         <v>539</v>
       </c>
@@ -13270,8 +14903,11 @@
       <c r="E540">
         <v>4</v>
       </c>
-    </row>
-    <row r="541" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F540">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="541" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
         <v>540</v>
       </c>
@@ -13287,8 +14923,11 @@
       <c r="E541">
         <v>4</v>
       </c>
-    </row>
-    <row r="542" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F541">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="542" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
         <v>541</v>
       </c>
@@ -13304,8 +14943,11 @@
       <c r="E542">
         <v>0</v>
       </c>
-    </row>
-    <row r="543" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F542">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="543" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
         <v>542</v>
       </c>
@@ -13321,8 +14963,11 @@
       <c r="E543">
         <v>1</v>
       </c>
-    </row>
-    <row r="544" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F543">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="544" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
         <v>543</v>
       </c>
@@ -13338,8 +14983,11 @@
       <c r="E544">
         <v>3</v>
       </c>
-    </row>
-    <row r="545" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F544">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="545" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
         <v>544</v>
       </c>
@@ -13355,8 +15003,11 @@
       <c r="E545">
         <v>2</v>
       </c>
-    </row>
-    <row r="546" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F545">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="546" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
         <v>545</v>
       </c>
@@ -13372,8 +15023,11 @@
       <c r="E546">
         <v>5</v>
       </c>
-    </row>
-    <row r="547" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F546">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="547" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
         <v>546</v>
       </c>
@@ -13389,8 +15043,11 @@
       <c r="E547">
         <v>5</v>
       </c>
-    </row>
-    <row r="548" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F547">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="548" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
         <v>547</v>
       </c>
@@ -13406,8 +15063,11 @@
       <c r="E548">
         <v>4</v>
       </c>
-    </row>
-    <row r="549" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F548">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="549" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
         <v>548</v>
       </c>
@@ -13423,8 +15083,11 @@
       <c r="E549">
         <v>4</v>
       </c>
-    </row>
-    <row r="550" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F549">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="550" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
         <v>549</v>
       </c>
@@ -13440,8 +15103,11 @@
       <c r="E550">
         <v>5</v>
       </c>
-    </row>
-    <row r="551" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F550">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="551" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
         <v>550</v>
       </c>
@@ -13457,8 +15123,11 @@
       <c r="E551">
         <v>1</v>
       </c>
-    </row>
-    <row r="552" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F551">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="552" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
         <v>551</v>
       </c>
@@ -13474,8 +15143,11 @@
       <c r="E552">
         <v>0</v>
       </c>
-    </row>
-    <row r="553" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F552">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="553" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
         <v>552</v>
       </c>
@@ -13491,8 +15163,11 @@
       <c r="E553">
         <v>3</v>
       </c>
-    </row>
-    <row r="554" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F553">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="554" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
         <v>553</v>
       </c>
@@ -13508,8 +15183,11 @@
       <c r="E554">
         <v>3</v>
       </c>
-    </row>
-    <row r="555" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F554">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="555" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
         <v>554</v>
       </c>
@@ -13525,8 +15203,11 @@
       <c r="E555">
         <v>0</v>
       </c>
-    </row>
-    <row r="556" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F555">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="556" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
         <v>555</v>
       </c>
@@ -13542,8 +15223,11 @@
       <c r="E556">
         <v>4</v>
       </c>
-    </row>
-    <row r="557" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F556">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="557" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
         <v>556</v>
       </c>
@@ -13559,8 +15243,11 @@
       <c r="E557">
         <v>0</v>
       </c>
-    </row>
-    <row r="558" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F557">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="558" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
         <v>557</v>
       </c>
@@ -13576,8 +15263,11 @@
       <c r="E558">
         <v>1</v>
       </c>
-    </row>
-    <row r="559" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F558">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="559" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
         <v>558</v>
       </c>
@@ -13593,8 +15283,11 @@
       <c r="E559">
         <v>0</v>
       </c>
-    </row>
-    <row r="560" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F559">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="560" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
         <v>559</v>
       </c>
@@ -13610,8 +15303,11 @@
       <c r="E560">
         <v>5</v>
       </c>
-    </row>
-    <row r="561" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F560">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="561" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
         <v>560</v>
       </c>
@@ -13627,8 +15323,11 @@
       <c r="E561">
         <v>4</v>
       </c>
-    </row>
-    <row r="562" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F561">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="562" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
         <v>561</v>
       </c>
@@ -13644,8 +15343,11 @@
       <c r="E562">
         <v>2</v>
       </c>
-    </row>
-    <row r="563" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F562">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="563" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
         <v>562</v>
       </c>
@@ -13661,8 +15363,11 @@
       <c r="E563">
         <v>0</v>
       </c>
-    </row>
-    <row r="564" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F563">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="564" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
         <v>563</v>
       </c>
@@ -13678,8 +15383,11 @@
       <c r="E564">
         <v>3</v>
       </c>
-    </row>
-    <row r="565" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F564">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="565" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
         <v>564</v>
       </c>
@@ -13695,8 +15403,11 @@
       <c r="E565">
         <v>5</v>
       </c>
-    </row>
-    <row r="566" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F565">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="566" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
         <v>565</v>
       </c>
@@ -13712,8 +15423,11 @@
       <c r="E566">
         <v>0</v>
       </c>
-    </row>
-    <row r="567" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F566">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="567" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
         <v>566</v>
       </c>
@@ -13729,8 +15443,11 @@
       <c r="E567">
         <v>2</v>
       </c>
-    </row>
-    <row r="568" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F567">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="568" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
         <v>567</v>
       </c>
@@ -13746,8 +15463,11 @@
       <c r="E568">
         <v>2</v>
       </c>
-    </row>
-    <row r="569" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F568">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="569" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
         <v>568</v>
       </c>
@@ -13763,8 +15483,11 @@
       <c r="E569">
         <v>0</v>
       </c>
-    </row>
-    <row r="570" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F569">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="570" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
         <v>569</v>
       </c>
@@ -13780,8 +15503,11 @@
       <c r="E570">
         <v>2</v>
       </c>
-    </row>
-    <row r="571" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F570">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="571" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
         <v>570</v>
       </c>
@@ -13797,8 +15523,11 @@
       <c r="E571">
         <v>2</v>
       </c>
-    </row>
-    <row r="572" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F571">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="572" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
         <v>571</v>
       </c>
@@ -13814,8 +15543,11 @@
       <c r="E572">
         <v>1</v>
       </c>
-    </row>
-    <row r="573" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F572">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="573" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
         <v>572</v>
       </c>
@@ -13831,8 +15563,11 @@
       <c r="E573">
         <v>3</v>
       </c>
-    </row>
-    <row r="574" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F573">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="574" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
         <v>573</v>
       </c>
@@ -13848,8 +15583,11 @@
       <c r="E574">
         <v>5</v>
       </c>
-    </row>
-    <row r="575" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F574">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="575" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
         <v>574</v>
       </c>
@@ -13865,8 +15603,11 @@
       <c r="E575">
         <v>0</v>
       </c>
-    </row>
-    <row r="576" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F575">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="576" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
         <v>575</v>
       </c>
@@ -13882,8 +15623,11 @@
       <c r="E576">
         <v>2</v>
       </c>
-    </row>
-    <row r="577" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F576">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="577" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
         <v>576</v>
       </c>
@@ -13899,8 +15643,11 @@
       <c r="E577">
         <v>5</v>
       </c>
-    </row>
-    <row r="578" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F577">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="578" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
         <v>577</v>
       </c>
@@ -13916,8 +15663,11 @@
       <c r="E578">
         <v>3</v>
       </c>
-    </row>
-    <row r="579" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F578">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="579" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
         <v>578</v>
       </c>
@@ -13933,8 +15683,11 @@
       <c r="E579">
         <v>2</v>
       </c>
-    </row>
-    <row r="580" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F579">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="580" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
         <v>579</v>
       </c>
@@ -13950,8 +15703,11 @@
       <c r="E580">
         <v>3</v>
       </c>
-    </row>
-    <row r="581" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F580">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="581" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
         <v>580</v>
       </c>
@@ -13967,8 +15723,11 @@
       <c r="E581">
         <v>5</v>
       </c>
-    </row>
-    <row r="582" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F581">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="582" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
         <v>581</v>
       </c>
@@ -13984,8 +15743,11 @@
       <c r="E582">
         <v>2</v>
       </c>
-    </row>
-    <row r="583" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F582">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="583" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
         <v>582</v>
       </c>
@@ -14001,8 +15763,11 @@
       <c r="E583">
         <v>4</v>
       </c>
-    </row>
-    <row r="584" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F583">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="584" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
         <v>583</v>
       </c>
@@ -14018,8 +15783,11 @@
       <c r="E584">
         <v>5</v>
       </c>
-    </row>
-    <row r="585" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F584">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="585" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
         <v>584</v>
       </c>
@@ -14035,8 +15803,11 @@
       <c r="E585">
         <v>5</v>
       </c>
-    </row>
-    <row r="586" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F585">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="586" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
         <v>585</v>
       </c>
@@ -14052,8 +15823,11 @@
       <c r="E586">
         <v>4</v>
       </c>
-    </row>
-    <row r="587" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F586">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="587" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
         <v>586</v>
       </c>
@@ -14069,8 +15843,11 @@
       <c r="E587">
         <v>5</v>
       </c>
-    </row>
-    <row r="588" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F587">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="588" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
         <v>587</v>
       </c>
@@ -14086,8 +15863,11 @@
       <c r="E588">
         <v>2</v>
       </c>
-    </row>
-    <row r="589" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F588">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="589" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
         <v>588</v>
       </c>
@@ -14103,8 +15883,11 @@
       <c r="E589">
         <v>0</v>
       </c>
-    </row>
-    <row r="590" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F589">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="590" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
         <v>589</v>
       </c>
@@ -14120,8 +15903,11 @@
       <c r="E590">
         <v>2</v>
       </c>
-    </row>
-    <row r="591" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F590">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="591" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
         <v>590</v>
       </c>
@@ -14137,8 +15923,11 @@
       <c r="E591">
         <v>0</v>
       </c>
-    </row>
-    <row r="592" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F591">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="592" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
         <v>591</v>
       </c>
@@ -14154,8 +15943,11 @@
       <c r="E592">
         <v>2</v>
       </c>
-    </row>
-    <row r="593" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F592">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="593" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
         <v>592</v>
       </c>
@@ -14171,8 +15963,11 @@
       <c r="E593">
         <v>3</v>
       </c>
-    </row>
-    <row r="594" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F593">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="594" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
         <v>593</v>
       </c>
@@ -14188,8 +15983,11 @@
       <c r="E594">
         <v>3</v>
       </c>
-    </row>
-    <row r="595" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F594">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="595" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
         <v>594</v>
       </c>
@@ -14205,8 +16003,11 @@
       <c r="E595">
         <v>4</v>
       </c>
-    </row>
-    <row r="596" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F595">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="596" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
         <v>595</v>
       </c>
@@ -14222,8 +16023,11 @@
       <c r="E596">
         <v>3</v>
       </c>
-    </row>
-    <row r="597" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F596">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="597" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
         <v>596</v>
       </c>
@@ -14239,8 +16043,11 @@
       <c r="E597">
         <v>3</v>
       </c>
-    </row>
-    <row r="598" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F597">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="598" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
         <v>597</v>
       </c>
@@ -14256,8 +16063,11 @@
       <c r="E598">
         <v>2</v>
       </c>
-    </row>
-    <row r="599" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F598">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="599" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
         <v>598</v>
       </c>
@@ -14273,8 +16083,11 @@
       <c r="E599">
         <v>2</v>
       </c>
-    </row>
-    <row r="600" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F599">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="600" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
         <v>599</v>
       </c>
@@ -14290,8 +16103,11 @@
       <c r="E600">
         <v>2</v>
       </c>
-    </row>
-    <row r="601" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F600">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="601" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
         <v>600</v>
       </c>
@@ -14307,8 +16123,11 @@
       <c r="E601">
         <v>0</v>
       </c>
-    </row>
-    <row r="602" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F601">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="602" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
         <v>601</v>
       </c>
@@ -14324,8 +16143,11 @@
       <c r="E602">
         <v>5</v>
       </c>
-    </row>
-    <row r="603" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F602">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="603" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
         <v>602</v>
       </c>
@@ -14341,8 +16163,11 @@
       <c r="E603">
         <v>2</v>
       </c>
-    </row>
-    <row r="604" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F603">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="604" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
         <v>603</v>
       </c>
@@ -14358,8 +16183,11 @@
       <c r="E604">
         <v>0</v>
       </c>
-    </row>
-    <row r="605" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F604">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="605" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
         <v>604</v>
       </c>
@@ -14375,8 +16203,11 @@
       <c r="E605">
         <v>3</v>
       </c>
-    </row>
-    <row r="606" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F605">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="606" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
         <v>605</v>
       </c>
@@ -14392,8 +16223,11 @@
       <c r="E606">
         <v>3</v>
       </c>
-    </row>
-    <row r="607" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F606">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="607" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
         <v>606</v>
       </c>
@@ -14409,8 +16243,11 @@
       <c r="E607">
         <v>2</v>
       </c>
-    </row>
-    <row r="608" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F607">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="608" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
         <v>607</v>
       </c>
@@ -14426,8 +16263,11 @@
       <c r="E608">
         <v>5</v>
       </c>
-    </row>
-    <row r="609" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F608">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="609" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
         <v>608</v>
       </c>
@@ -14443,8 +16283,11 @@
       <c r="E609">
         <v>2</v>
       </c>
-    </row>
-    <row r="610" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F609">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="610" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
         <v>609</v>
       </c>
@@ -14460,8 +16303,11 @@
       <c r="E610">
         <v>3</v>
       </c>
-    </row>
-    <row r="611" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F610">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="611" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
         <v>610</v>
       </c>
@@ -14477,8 +16323,11 @@
       <c r="E611">
         <v>0</v>
       </c>
-    </row>
-    <row r="612" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F611">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="612" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
         <v>611</v>
       </c>
@@ -14494,8 +16343,11 @@
       <c r="E612">
         <v>2</v>
       </c>
-    </row>
-    <row r="613" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F612">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="613" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
         <v>612</v>
       </c>
@@ -14511,8 +16363,11 @@
       <c r="E613">
         <v>2</v>
       </c>
-    </row>
-    <row r="614" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F613">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="614" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
         <v>613</v>
       </c>
@@ -14528,8 +16383,11 @@
       <c r="E614">
         <v>0</v>
       </c>
-    </row>
-    <row r="615" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F614">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="615" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
         <v>614</v>
       </c>
@@ -14545,8 +16403,11 @@
       <c r="E615">
         <v>0</v>
       </c>
-    </row>
-    <row r="616" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F615">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="616" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
         <v>615</v>
       </c>
@@ -14562,8 +16423,11 @@
       <c r="E616">
         <v>4</v>
       </c>
-    </row>
-    <row r="617" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F616">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="617" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
         <v>616</v>
       </c>
@@ -14579,8 +16443,11 @@
       <c r="E617">
         <v>1</v>
       </c>
-    </row>
-    <row r="618" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F617">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="618" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
         <v>617</v>
       </c>
@@ -14596,8 +16463,11 @@
       <c r="E618">
         <v>4</v>
       </c>
-    </row>
-    <row r="619" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F618">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="619" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
         <v>618</v>
       </c>
@@ -14613,8 +16483,11 @@
       <c r="E619">
         <v>2</v>
       </c>
-    </row>
-    <row r="620" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F619">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="620" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
         <v>619</v>
       </c>
@@ -14630,8 +16503,11 @@
       <c r="E620">
         <v>4</v>
       </c>
-    </row>
-    <row r="621" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F620">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="621" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
         <v>620</v>
       </c>
@@ -14647,8 +16523,11 @@
       <c r="E621">
         <v>0</v>
       </c>
-    </row>
-    <row r="622" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F621">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="622" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
         <v>621</v>
       </c>
@@ -14664,8 +16543,11 @@
       <c r="E622">
         <v>5</v>
       </c>
-    </row>
-    <row r="623" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F622">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="623" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
         <v>622</v>
       </c>
@@ -14681,8 +16563,11 @@
       <c r="E623">
         <v>3</v>
       </c>
-    </row>
-    <row r="624" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F623">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="624" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
         <v>623</v>
       </c>
@@ -14698,8 +16583,11 @@
       <c r="E624">
         <v>0</v>
       </c>
-    </row>
-    <row r="625" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F624">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="625" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
         <v>624</v>
       </c>
@@ -14715,8 +16603,11 @@
       <c r="E625">
         <v>2</v>
       </c>
-    </row>
-    <row r="626" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F625">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="626" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
         <v>625</v>
       </c>
@@ -14732,8 +16623,11 @@
       <c r="E626">
         <v>3</v>
       </c>
-    </row>
-    <row r="627" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F626">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="627" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
         <v>626</v>
       </c>
@@ -14748,6 +16642,9 @@
       </c>
       <c r="E627">
         <v>2</v>
+      </c>
+      <c r="F627">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
